--- a/code/MAS_Entwickler_Dashboard_final_third_run.xlsx
+++ b/code/MAS_Entwickler_Dashboard_final_third_run.xlsx
@@ -513,7 +513,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Der Bauplan gibt an, dass die Entscheidung 'TABLE' ist, was bedeutet, dass ein Tabellenaufruf generiert werden muss. Die Bedingungsspalte ist 'K40_FG_AF', und die Zielmerkmal ist 'K40_BRM'. Die Zeilen-Daten zeigen die Zuordnung von 'K40_FG_AF' zu 'K40_BRM'. Die 'original_code_mapping' zeigt die Logik, die in der Tabelle abgebildet werden muss.</t>
+          <t>Der Bauplan gibt an, dass die Entscheidung 'TABLE' ist, was bedeutet, dass ein Tabellenaufruf generiert werden muss. Die Bedingungsspalte ist 'K40_FG_AF', und die Zielspalte ist 'K40_BRM'. Die Zeilen-Daten zeigen die Zuordnung von 'K40_FG_AF' zu 'K40_BRM'. Die 'original_code_mapping' wird ignoriert, da die Entscheidung 'TABLE' ist.</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Da die Entscheidung 'TABLE' ist, muss ein Tabellenaufruf generiert werden. Die Bedingungs-Spalten sind 'K40_ABL' und 'K40_FG_AF'. Die Zeilen-Daten geben die möglichen Werte für das Zielmerkmal 'K40_KO' basierend auf den Bedingungen an. Die Logik aus 'original_code_mapping' zeigt, dass alle Bedingungen identisch sind, daher wird eine Tabelle verwendet.</t>
+          <t>Da die Entscheidung 'TABLE' ist, muss ein Tabellenaufruf generiert werden. Die Bedingungsspalten sind 'K40_ABL' und 'K40_FG_AF'. Die Zeilen enthalten die Werte für diese Spalten und das Zielmerkmal 'K40_KO'. Die Logik aus 'original_code_mapping' wird ignoriert, da die Tabelle verwendet wird.</t>
         </is>
       </c>
     </row>
@@ -806,7 +806,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Der Bauplan hat die Entscheidung 'TABLE', daher muss ein Tabellenaufruf generiert werden. Die Bedingungs-Spalten sind 'K40_FG_AF' und 'K40_TS', und die Zielmerkmal-Zuweisung ist 'K40_KO'. Die Zeilen-Daten enthalten die Werte '06', '05' und '07', die jeweils mit den Bedingungen aus 'original_code_mapping' übereinstimmen. Da die Entscheidung 'TABLE' ist, wird ein Tabellenaufruf erstellt, der die Bedingungs-Spalten und die entsprechenden Werte verwendet.</t>
+          <t>Der Bauplan hat die Entscheidung 'TABLE', daher muss ein Tabellenaufruf generiert werden. Die Bedingungs-Spalten sind 'K40_FG_AF' und 'K40_TS', und die Zielmerkmal-Zuweisung ist 'K40_KO'. Die Zeilen-Daten enthalten die Werte, die in der Tabelle verwendet werden sollen. Die Logik aus 'original_code_mapping' wird ignoriert, da die Entscheidung 'TABLE' ist.</t>
         </is>
       </c>
     </row>
@@ -828,6 +828,11 @@
       <c r="B9" s="4" t="inlineStr">
         <is>
           <t>K40_TS</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>K40_KO</t>
         </is>
       </c>
     </row>
@@ -955,7 +960,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Der Bauplan hat die Entscheidung 'NO_TABLE', daher wird für jeden Eintrag aus 'original_code_mapping' ein Standalone IF-Statement generiert. Die Logik wird gemäß den AVC-Syntax-Regeln übersetzt.</t>
+          <t>Da die Entscheidung 'NO_TABLE' ist, generiere ich Standalone AVC Code basierend auf den 'original_code_mapping' Einträgen. Ich übersetze die Logik in AVC Syntax und nutze das 'echtes_zielmerkmal' für die Zuweisungen.</t>
         </is>
       </c>
     </row>
@@ -978,10 +983,10 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>K40_KO = '09' IF (SPECIFIED(K40_fg_af) AND K40_fg_af = '1' AND K40_brm = '0' AND K40_ts &lt;&gt; '1' AND (K40_pl IN ('d1','d2') OR K40_pl IN ('H1','H3')) AND K40_abl = '0').
+          <t>K40_KO = '09' IF (SPECIFIED(K40_fg_af) AND K40_fg_af = '1' AND K40_brm = '0' AND K40_ts &lt;&gt; '1' AND (K40_pl IN ('d1', 'd2') OR K40_pl IN ('H1', 'H3')) AND K40_abl = '0').
 K40_KO = '10' IF (SPECIFIED(True)).
 K40_KO = '08' IF ((K40_fg_af = '3' OR K40_fg_af = '4') AND K40_brm = '0' AND K40_ts &lt;&gt; '1').
-K40_KO = '99' IF (K40_pl IN ('d1','h1','h2')).</t>
+K40_KO = '99' IF (K40_pl IN ('d1', 'h1', 'h2')).</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1049,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Der Bauplan hat die Entscheidung 'NO_TABLE', daher wird für jede Logik aus 'original_code_mapping' ein separates IF-Statement erstellt. Die Logik wird direkt aus 'original_code_mapping' übernommen und in AVC Syntax übersetzt.</t>
+          <t>Der Bauplan hat die Entscheidung 'NO_TABLE', daher wird für jeden Eintrag in 'original_code_mapping' ein separates IF-Statement generiert. Die Logik aus 'original_code_mapping' wird direkt in die AVC Syntax übersetzt, wobei die Operatoren in Großbuchstaben geschrieben werden und 'specified Merkmal' in 'SPECIFIED(Merkmal)' übersetzt wird.</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1072,7 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>K40_ROD = '200' IF (K40_fst = '0' AND K40_brm = '0' AND K40_abl = '0' AND K40_fg_af IN ('1','2') AND K40_ko_af IN ('0','1','2','4') AND K40_dsb = '0' AND [UNCLASSIFIED_T32_BRM] = '0' OR K40_fst = '0' AND K40_brm = '0' AND K40_abl = '0' AND K40_fg_af IN ('3','4') AND K40_ko_af IN ('2','3') AND K40_dsb = '0' AND [UNCLASSIFIED_T32_BRM] = '0'). K40_ROD = '125' IF (SPECIFIED(K40_fst) AND K40_fst = '1' AND K40_brm = '0' AND K40_fg_af IN ('1','2') AND K40_pl IN ('d2','h3')).</t>
+          <t>K40_ROD = '200' IF ((K40_fst = '0' AND K40_brm = '0' AND K40_abl = '0' AND K40_fg_af IN ('1','2') AND K40_ko_af IN ('0','1','2','4') AND K40_dsb = '0' AND [UNCLASSIFIED_T32_BRM] = '0') OR (K40_fst = '0' AND K40_brm = '0' AND K40_abl = '0' AND K40_fg_af IN ('3','4') AND K40_ko_af IN ('2','3') AND K40_dsb = '0' AND [UNCLASSIFIED_T32_BRM] = '0')). K40_ROD = '125' IF (SPECIFIED(K40_fst) AND K40_fst = '1' AND K40_brm = '0' AND K40_fg_af IN ('1','2') AND K40_pl IN ('d2','h3')).</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1135,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Der Bauplan hat die Entscheidung 'NO_TABLE', was bedeutet, dass ich für jeden Eintrag aus 'original_code_mapping' ein sauberes IF-Statement nach AVC Syntax erstellen muss. Ich werde die Logik aus 'original_code_mapping' verwenden, um die Bedingungen zu formulieren und die Zuweisungen gemäß den Regeln für Standalone-Code zu schreiben.</t>
+          <t>Der Bauplan hat die Entscheidung 'NO_TABLE', daher müssen wir für jeden Eintrag aus 'original_code_mapping' ein sauberes IF-Statement nach AVC Syntax erstellen. Die Logik aus 'original_code_mapping' wird direkt in die IF-Bedingungen übersetzt, wobei die Syntax-Regeln strikt eingehalten werden.</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1246,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Der Bauplan hat die Entscheidung 'NO_TABLE', was bedeutet, dass ich für jeden Eintrag aus 'original_code_mapping' ein sauberes IF-Statement nach AVC Syntax erstellen muss. Ich nutze die echte Logik aus 'original_code_mapping' und übersetze sie gemäß den AVC-Syntax-Regeln. Die Zuweisungen erfolgen immer nach dem Muster 'Zuweisung IF Bedingung.'</t>
+          <t>Der Bauplan hat die Entscheidung 'NO_TABLE', daher müssen wir für jeden Eintrag in 'original_code_mapping' ein separates IF-Statement generieren. Die Logik aus 'original_code_mapping' wird direkt in die AVC Syntax übersetzt, wobei 'ne' in '&lt;&gt;' und 'specified Merkmal' in 'SPECIFIED(Merkmal)' umgewandelt wird. Die Zuweisung erfolgt gemäß der Regel 'Zuweisung IF Bedingung'.</t>
         </is>
       </c>
     </row>
@@ -1264,12 +1269,12 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>K40_PS = 'PS03' IF (SPECIFIED(K40_rod) AND SPECIFIED(K40_fg_af) AND SPECIFIED(K40_schp) AND SPECIFIED(K40_ko) AND K40_rod &lt; '200' AND K40_fg_af &lt; '3' AND (K40_schp = '04' OR K40_schp = '06') AND K40_ko &lt;&gt; '09').
-K40_PS = 'PW04' IF (SPECIFIED(K40_rod) AND SPECIFIED(K40_fg_af) AND SPECIFIED(K40_schp) AND SPECIFIED(K40_ko) AND SPECIFIED(K40_abl) AND K40_rod &lt; '200' AND K40_fg_af &lt; '3' AND (K40_schp = '04' OR K40_schp = '06') AND K40_ko &lt;&gt; '09' AND K40_fg_af &lt; '0' AND K40_abl = '0').
-K40_PS = 'PS12' IF (SPECIFIED(K40_abl) AND SPECIFIED(K40_ko) AND K40_abl = '0' AND K40_ko &lt;&gt; '09').
-K40_PS = 'PS13' IF (SPECIFIED(K40_abl) AND SPECIFIED(K40_ko) AND K40_abl = '0' AND K40_ko &lt;&gt; '09').
-K40_PS = 'PS06' IF (SPECIFIED(K40_ko) AND K40_ko &lt;&gt; '09').
-K40_PS = 'PW08' IF (SPECIFIED(K40_abl) AND K40_abl = '0').</t>
+          <t>K40_PS = 'PS03' IF (TRUE AND K40_rod &lt; '200' AND K40_fg_af &lt; '3' AND (K40_schp = '04' OR K40_schp = '06') AND K40_ko &lt;&gt; '09').
+K40_PS = 'PW04' IF (K40_rod &lt; '200' AND K40_fg_af &lt; '3' AND (K40_schp = '04' OR K40_schp = '06') AND K40_ko &lt;&gt; '09' AND K40_fg_af &lt; '0' AND K40_abl = '0').
+K40_PS = 'PS12' IF (K40_abl = '0' AND K40_ko &lt;&gt; '09').
+K40_PS = 'PS13' IF (K40_abl = '0' AND K40_ko &lt;&gt; '09').
+K40_PS = 'PS06' IF (K40_ko &lt;&gt; '09').
+K40_PS = 'PW08' IF (K40_abl = '0').</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1337,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Der Bauplan hat die Entscheidung 'NO_TABLE', was bedeutet, dass ich für jeden Eintrag aus 'original_code_mapping' ein sauberes IF-Statement nach AVC Syntax erstellen muss. Ich nutze die echte Logik aus 'original_code_mapping' und übersetze sie gemäß den AVC-Syntax-Regeln.</t>
+          <t>Da die Entscheidung 'NO_TABLE' ist, müssen wir für jeden Eintrag aus 'original_code_mapping' ein sauberes IF-Statement nach AVC Syntax erstellen. Die Zuweisung erfolgt immer nach dem Muster 'Zuweisung IF Bedingung.' und wir nutzen für die Zuweisung immer das 'echtes_zielmerkmal', welches 'PS' ist.</t>
         </is>
       </c>
     </row>
